--- a/salidas/empresas/DELL.xlsx
+++ b/salidas/empresas/DELL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B2" t="n">
-        <v>11.39071273803711</v>
+        <v>11.39071178436279</v>
       </c>
       <c r="C2" t="n">
         <v>12.53915691375732</v>
@@ -507,11 +519,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B3" t="n">
-        <v>12.18612480163574</v>
+        <v>12.18612670898438</v>
       </c>
       <c r="C3" t="n">
         <v>13.41476535797119</v>
@@ -532,11 +544,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B4" t="n">
-        <v>12.51499843597412</v>
+        <v>12.5149974822998</v>
       </c>
       <c r="C4" t="n">
         <v>13.77679538726807</v>
@@ -557,11 +569,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B5" t="n">
-        <v>13.65457820892334</v>
+        <v>13.65458011627197</v>
       </c>
       <c r="C5" t="n">
         <v>15.03127193450928</v>
@@ -582,7 +594,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B6" t="n">
@@ -607,11 +619,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B7" t="n">
-        <v>16.05866050720215</v>
+        <v>16.05865859985352</v>
       </c>
       <c r="C7" t="n">
         <v>17.6777400970459</v>
@@ -632,11 +644,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B8" t="n">
-        <v>16.18613433837891</v>
+        <v>16.18613243103027</v>
       </c>
       <c r="C8" t="n">
         <v>17.81806373596191</v>
@@ -657,11 +669,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B9" t="n">
-        <v>16.33654594421387</v>
+        <v>16.33654403686523</v>
       </c>
       <c r="C9" t="n">
         <v>17.983642578125</v>
@@ -682,11 +694,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B10" t="n">
-        <v>17.10901641845703</v>
+        <v>17.10901069641113</v>
       </c>
       <c r="C10" t="n">
         <v>18.83399391174316</v>
@@ -707,11 +719,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B11" t="n">
-        <v>17.69027709960938</v>
+        <v>17.69028282165527</v>
       </c>
       <c r="C11" t="n">
         <v>19.47386169433594</v>
@@ -732,11 +744,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B12" t="n">
-        <v>15.57937526702881</v>
+        <v>15.57937812805176</v>
       </c>
       <c r="C12" t="n">
         <v>17.15013122558594</v>
@@ -757,11 +769,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B13" t="n">
-        <v>16.38498497009277</v>
+        <v>16.38498687744141</v>
       </c>
       <c r="C13" t="n">
         <v>18.03696441650391</v>
@@ -782,7 +794,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B14" t="n">
@@ -807,11 +819,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B15" t="n">
-        <v>19.68390655517578</v>
+        <v>19.68390846252441</v>
       </c>
       <c r="C15" t="n">
         <v>21.66849327087402</v>
@@ -832,11 +844,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B16" t="n">
-        <v>21.10137557983398</v>
+        <v>21.10137176513672</v>
       </c>
       <c r="C16" t="n">
         <v>23.22887229919434</v>
@@ -857,11 +869,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B17" t="n">
-        <v>19.94649887084961</v>
+        <v>19.94649505615234</v>
       </c>
       <c r="C17" t="n">
         <v>21.95755767822266</v>
@@ -882,11 +894,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B18" t="n">
-        <v>20.72151184082031</v>
+        <v>20.72150993347168</v>
       </c>
       <c r="C18" t="n">
         <v>22.81071281433105</v>
@@ -907,7 +919,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B19" t="n">
@@ -932,11 +944,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B20" t="n">
-        <v>18.93948364257812</v>
+        <v>18.93948173522949</v>
       </c>
       <c r="C20" t="n">
         <v>20.84901428222656</v>
@@ -957,7 +969,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B21" t="n">
@@ -982,11 +994,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B22" t="n">
-        <v>18.29703521728516</v>
+        <v>18.29703712463379</v>
       </c>
       <c r="C22" t="n">
         <v>20.14179229736328</v>
@@ -1007,11 +1019,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B23" t="n">
-        <v>20.56344985961914</v>
+        <v>20.56345176696777</v>
       </c>
       <c r="C23" t="n">
         <v>22.63671493530273</v>
@@ -1032,11 +1044,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B24" t="n">
-        <v>21.56281661987305</v>
+        <v>21.56281471252441</v>
       </c>
       <c r="C24" t="n">
         <v>23.73683738708496</v>
@@ -1057,11 +1069,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B25" t="n">
-        <v>23.58703994750977</v>
+        <v>23.5870361328125</v>
       </c>
       <c r="C25" t="n">
         <v>25.96514701843262</v>
@@ -1082,11 +1094,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B26" t="n">
-        <v>24.5175666809082</v>
+        <v>24.51756858825684</v>
       </c>
       <c r="C26" t="n">
         <v>26.9894962310791</v>
@@ -1107,11 +1119,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B27" t="n">
-        <v>24.75976181030273</v>
+        <v>24.7597599029541</v>
       </c>
       <c r="C27" t="n">
         <v>27.25610733032227</v>
@@ -1132,11 +1144,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B28" t="n">
-        <v>23.04401969909668</v>
+        <v>23.04401206970215</v>
       </c>
       <c r="C28" t="n">
         <v>25.36737632751465</v>
@@ -1157,7 +1169,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B29" t="n">
@@ -1182,11 +1194,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B30" t="n">
-        <v>22.50078964233398</v>
+        <v>22.50079345703125</v>
       </c>
       <c r="C30" t="n">
         <v>24.76938629150391</v>
@@ -1207,7 +1219,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B31" t="n">
@@ -1232,11 +1244,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B32" t="n">
-        <v>25.70072364807129</v>
+        <v>25.70071983337402</v>
       </c>
       <c r="C32" t="n">
         <v>28.29194068908691</v>
@@ -1257,11 +1269,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B33" t="n">
-        <v>27.02213096618652</v>
+        <v>27.02213287353516</v>
       </c>
       <c r="C33" t="n">
         <v>29.74657821655273</v>
@@ -1282,11 +1294,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B34" t="n">
-        <v>31.03700828552246</v>
+        <v>31.03700256347656</v>
       </c>
       <c r="C34" t="n">
         <v>34.16624450683594</v>
@@ -1307,11 +1319,11 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B35" t="n">
-        <v>27.41809463500977</v>
+        <v>27.41810035705566</v>
       </c>
       <c r="C35" t="n">
         <v>30.18246269226074</v>
@@ -1332,11 +1344,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B36" t="n">
-        <v>23.38940620422363</v>
+        <v>23.389404296875</v>
       </c>
       <c r="C36" t="n">
         <v>25.74759292602539</v>
@@ -1357,11 +1369,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B37" t="n">
-        <v>26.58473014831543</v>
+        <v>26.5847339630127</v>
       </c>
       <c r="C37" t="n">
         <v>29.26507949829102</v>
@@ -1382,11 +1394,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B38" t="n">
-        <v>23.72551536560059</v>
+        <v>23.72551155090332</v>
       </c>
       <c r="C38" t="n">
         <v>26.11758613586426</v>
@@ -1407,11 +1419,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B39" t="n">
-        <v>23.8774528503418</v>
+        <v>23.87745475769043</v>
       </c>
       <c r="C39" t="n">
         <v>26.28484535217285</v>
@@ -1432,7 +1444,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B40" t="n">
@@ -1457,7 +1469,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B41" t="n">
@@ -1482,7 +1494,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B42" t="n">
@@ -1507,11 +1519,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B43" t="n">
-        <v>22.45475196838379</v>
+        <v>22.45475578308105</v>
       </c>
       <c r="C43" t="n">
         <v>24.71870231628418</v>
@@ -1532,11 +1544,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B44" t="n">
-        <v>18.6286506652832</v>
+        <v>18.62864303588867</v>
       </c>
       <c r="C44" t="n">
         <v>20.5068416595459</v>
@@ -1557,11 +1569,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B45" t="n">
-        <v>18.20966911315918</v>
+        <v>18.20966720581055</v>
       </c>
       <c r="C45" t="n">
         <v>20.04561614990234</v>
@@ -1586,11 +1598,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B46" t="n">
-        <v>19.6553840637207</v>
+        <v>19.65538787841797</v>
       </c>
       <c r="C46" t="n">
         <v>21.63710021972656</v>
@@ -1615,7 +1627,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B47" t="n">
@@ -1644,7 +1656,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B48" t="n">
@@ -1673,11 +1685,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B49" t="n">
-        <v>27.54701232910156</v>
+        <v>27.54701805114746</v>
       </c>
       <c r="C49" t="n">
         <v>30.32437896728516</v>
@@ -1702,11 +1714,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B50" t="n">
-        <v>30.42464828491211</v>
+        <v>30.42465019226074</v>
       </c>
       <c r="C50" t="n">
         <v>33.49214553833008</v>
@@ -1731,11 +1743,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B51" t="n">
-        <v>31.16592788696289</v>
+        <v>31.16592407226562</v>
       </c>
       <c r="C51" t="n">
         <v>34.30815887451172</v>
@@ -1760,11 +1772,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B52" t="n">
-        <v>27.74499702453613</v>
+        <v>27.74499320983887</v>
       </c>
       <c r="C52" t="n">
         <v>30.54232025146484</v>
@@ -1789,11 +1801,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B53" t="n">
-        <v>31.78289604187012</v>
+        <v>31.78289413452148</v>
       </c>
       <c r="C53" t="n">
         <v>34.98732757568359</v>
@@ -1818,11 +1830,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B54" t="n">
-        <v>33.74428176879883</v>
+        <v>33.74428558349609</v>
       </c>
       <c r="C54" t="n">
         <v>37.14647674560547</v>
@@ -1847,11 +1859,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B55" t="n">
-        <v>33.56012344360352</v>
+        <v>33.56011581420898</v>
       </c>
       <c r="C55" t="n">
         <v>36.94374084472656</v>
@@ -1876,11 +1888,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B56" t="n">
-        <v>37.32637023925781</v>
+        <v>37.32636260986328</v>
       </c>
       <c r="C56" t="n">
         <v>41.0897102355957</v>
@@ -1905,11 +1917,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B57" t="n">
-        <v>40.58614730834961</v>
+        <v>40.58614349365234</v>
       </c>
       <c r="C57" t="n">
         <v>44.67815399169922</v>
@@ -1934,11 +1946,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B58" t="n">
-        <v>45.27323150634766</v>
+        <v>45.27324295043945</v>
       </c>
       <c r="C58" t="n">
         <v>49.83781051635742</v>
@@ -1963,11 +1975,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B59" t="n">
-        <v>45.41596221923828</v>
+        <v>45.41596603393555</v>
       </c>
       <c r="C59" t="n">
         <v>49.99493026733398</v>
@@ -1992,11 +2004,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B60" t="n">
-        <v>45.89020156860352</v>
+        <v>45.89020538330078</v>
       </c>
       <c r="C60" t="n">
         <v>50.5169792175293</v>
@@ -2021,11 +2033,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B61" t="n">
-        <v>44.48591613769531</v>
+        <v>44.48591995239258</v>
       </c>
       <c r="C61" t="n">
         <v>48.97111129760742</v>
@@ -2050,11 +2062,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B62" t="n">
-        <v>44.87267684936523</v>
+        <v>44.8726806640625</v>
       </c>
       <c r="C62" t="n">
         <v>49.39685821533203</v>
@@ -2079,11 +2091,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B63" t="n">
-        <v>47.90224456787109</v>
+        <v>47.90225219726562</v>
       </c>
       <c r="C63" t="n">
         <v>52.73188018798828</v>
@@ -2108,11 +2120,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B64" t="n">
-        <v>50.64174652099609</v>
+        <v>50.64175796508789</v>
       </c>
       <c r="C64" t="n">
         <v>55.74759292602539</v>
@@ -2137,11 +2149,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B65" t="n">
-        <v>51.29800033569336</v>
+        <v>51.29799652099609</v>
       </c>
       <c r="C65" t="n">
         <v>56.47000122070312</v>
@@ -2166,7 +2178,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B66" t="n">
@@ -2195,11 +2207,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B67" t="n">
-        <v>51.60686492919922</v>
+        <v>51.60686111450195</v>
       </c>
       <c r="C67" t="n">
         <v>56.81000137329102</v>
@@ -2224,11 +2236,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B68" t="n">
-        <v>46.29264831542969</v>
+        <v>46.29264068603516</v>
       </c>
       <c r="C68" t="n">
         <v>50.95999908447266</v>
@@ -2253,7 +2265,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B69" t="n">
@@ -2282,11 +2294,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B70" t="n">
-        <v>43.00356292724609</v>
+        <v>43.00356674194336</v>
       </c>
       <c r="C70" t="n">
         <v>47.0099983215332</v>
@@ -2311,11 +2323,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B71" t="n">
-        <v>45.6838493347168</v>
+        <v>45.68384552001953</v>
       </c>
       <c r="C71" t="n">
         <v>49.93999862670898</v>
@@ -2340,11 +2352,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B72" t="n">
-        <v>42.27174758911133</v>
+        <v>42.27173233032227</v>
       </c>
       <c r="C72" t="n">
         <v>46.20999908447266</v>
@@ -2369,11 +2381,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B73" t="n">
-        <v>41.53928756713867</v>
+        <v>41.53929138183594</v>
       </c>
       <c r="C73" t="n">
         <v>45.06000137329102</v>
@@ -2398,11 +2410,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B74" t="n">
-        <v>35.29824829101562</v>
+        <v>35.29825210571289</v>
       </c>
       <c r="C74" t="n">
         <v>38.29000091552734</v>
@@ -2427,11 +2439,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B75" t="n">
-        <v>31.50016021728516</v>
+        <v>31.50016784667969</v>
       </c>
       <c r="C75" t="n">
         <v>34.16999816894531</v>
@@ -2456,11 +2468,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B76" t="n">
-        <v>35.74182891845703</v>
+        <v>35.7418327331543</v>
       </c>
       <c r="C76" t="n">
         <v>38.40000152587891</v>
@@ -2485,11 +2497,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B77" t="n">
-        <v>41.68950271606445</v>
+        <v>41.68949890136719</v>
       </c>
       <c r="C77" t="n">
         <v>44.79000091552734</v>
@@ -2514,11 +2526,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B78" t="n">
-        <v>37.43585205078125</v>
+        <v>37.43585586547852</v>
       </c>
       <c r="C78" t="n">
         <v>40.22000122070312</v>
@@ -2543,11 +2555,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B79" t="n">
-        <v>38.11463928222656</v>
+        <v>38.11463165283203</v>
       </c>
       <c r="C79" t="n">
         <v>40.61999893188477</v>
@@ -2572,11 +2584,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B80" t="n">
-        <v>38.13340377807617</v>
+        <v>38.13339996337891</v>
       </c>
       <c r="C80" t="n">
         <v>40.63999938964844</v>
@@ -2601,11 +2613,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B81" t="n">
-        <v>37.72992706298828</v>
+        <v>37.72993087768555</v>
       </c>
       <c r="C81" t="n">
         <v>40.20999908447266</v>
@@ -2630,7 +2642,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B82" t="n">
@@ -2659,11 +2671,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B83" t="n">
-        <v>42.41020965576172</v>
+        <v>42.41020584106445</v>
       </c>
       <c r="C83" t="n">
         <v>44.81000137329102</v>
@@ -2688,11 +2700,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B84" t="n">
-        <v>51.21213912963867</v>
+        <v>51.21214294433594</v>
       </c>
       <c r="C84" t="n">
         <v>54.11000061035156</v>
@@ -2717,7 +2729,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B85" t="n">
@@ -2746,11 +2758,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B86" t="n">
-        <v>53.59833145141602</v>
+        <v>53.59833526611328</v>
       </c>
       <c r="C86" t="n">
         <v>56.2400016784668</v>
@@ -2775,11 +2787,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B87" t="n">
-        <v>65.66368103027344</v>
+        <v>65.66366577148438</v>
       </c>
       <c r="C87" t="n">
         <v>68.90000152587891</v>
@@ -2804,11 +2816,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B88" t="n">
-        <v>64.12713623046875</v>
+        <v>64.12714385986328</v>
       </c>
       <c r="C88" t="n">
         <v>66.91000366210938</v>
@@ -2833,11 +2845,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B89" t="n">
-        <v>72.71449279785156</v>
+        <v>72.71448516845703</v>
       </c>
       <c r="C89" t="n">
         <v>75.87000274658203</v>
@@ -2862,11 +2874,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B90" t="n">
-        <v>73.31827545166016</v>
+        <v>73.31828308105469</v>
       </c>
       <c r="C90" t="n">
         <v>76.5</v>
@@ -2891,11 +2903,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B91" t="n">
-        <v>79.78778839111328</v>
+        <v>79.78779602050781</v>
       </c>
       <c r="C91" t="n">
         <v>82.87999725341797</v>
@@ -2920,11 +2932,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B92" t="n">
-        <v>91.12828826904297</v>
+        <v>91.1282958984375</v>
       </c>
       <c r="C92" t="n">
         <v>94.66000366210938</v>
@@ -2949,7 +2961,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B93" t="n">
@@ -2978,7 +2990,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B94" t="n">
@@ -3007,11 +3019,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B95" t="n">
-        <v>134.8755950927734</v>
+        <v>134.8755798339844</v>
       </c>
       <c r="C95" t="n">
         <v>139.5599975585938</v>
@@ -3036,7 +3048,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B96" t="n">
@@ -3065,11 +3077,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B97" t="n">
-        <v>110.2453460693359</v>
+        <v>110.2453536987305</v>
       </c>
       <c r="C97" t="n">
         <v>113.6800003051758</v>
@@ -3094,7 +3106,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B98" t="n">
@@ -3123,11 +3135,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B99" t="n">
-        <v>114.9585113525391</v>
+        <v>114.9585037231445</v>
       </c>
       <c r="C99" t="n">
         <v>118.5400009155273</v>
@@ -3152,7 +3164,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B100" t="n">
@@ -3181,11 +3193,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B101" t="n">
-        <v>124.1748123168945</v>
+        <v>124.1748046875</v>
       </c>
       <c r="C101" t="n">
         <v>127.5899963378906</v>
@@ -3210,11 +3222,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B102" t="n">
-        <v>112.1553955078125</v>
+        <v>112.155387878418</v>
       </c>
       <c r="C102" t="n">
         <v>115.2399978637695</v>
@@ -3239,11 +3251,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B103" t="n">
-        <v>101.2307891845703</v>
+        <v>101.2307815551758</v>
       </c>
       <c r="C103" t="n">
         <v>103.5999984741211</v>
@@ -3268,11 +3280,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B104" t="n">
-        <v>100.4100112915039</v>
+        <v>100.4100036621094</v>
       </c>
       <c r="C104" t="n">
         <v>102.7600021362305</v>
@@ -3297,11 +3309,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B105" t="n">
-        <v>89.06549835205078</v>
+        <v>89.06550598144531</v>
       </c>
       <c r="C105" t="n">
         <v>91.15000152587891</v>
@@ -3326,7 +3338,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B106" t="n">
@@ -3355,7 +3367,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B107" t="n">
@@ -3384,7 +3396,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B108" t="n">
@@ -3413,11 +3425,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B109" t="n">
-        <v>131.0204162597656</v>
+        <v>131.0204010009766</v>
       </c>
       <c r="C109" t="n">
         <v>132.6900024414062</v>
@@ -3442,7 +3454,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B110" t="n">
@@ -3471,7 +3483,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B111" t="n">
@@ -3500,11 +3512,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B112" t="n">
-        <v>160.5414733886719</v>
+        <v>160.5414581298828</v>
       </c>
       <c r="C112" t="n">
         <v>162.0099945068359</v>
@@ -3529,11 +3541,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B113" t="n">
-        <v>132.1412811279297</v>
+        <v>132.1412658691406</v>
       </c>
       <c r="C113" t="n">
         <v>133.3500061035156</v>
@@ -3558,7 +3570,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B114" t="n">
@@ -3587,7 +3599,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B115" t="n">
@@ -3616,7 +3628,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B116" t="n">
@@ -3645,7 +3657,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B117" t="n">
@@ -3674,7 +3686,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B118" t="n">
@@ -3703,7 +3715,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B119" t="n">
@@ -3732,7 +3744,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B120" t="n">
@@ -3761,7 +3773,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B121" t="n">
@@ -3790,7 +3802,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B122" t="n">
@@ -3819,32 +3831,32 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B123" t="n">
-        <v>549.8300170898438</v>
+        <v>536.02001953125</v>
       </c>
       <c r="C123" t="n">
-        <v>549.8300170898438</v>
+        <v>536.02001953125</v>
       </c>
       <c r="D123" t="n">
-        <v>197409800</v>
+        <v>205362100</v>
       </c>
       <c r="E123" t="n">
         <v>17.19</v>
       </c>
       <c r="F123" t="n">
-        <v>31.9854576550229</v>
+        <v>31.18208374236475</v>
       </c>
       <c r="G123" t="n">
         <v>640000000</v>
       </c>
       <c r="H123" t="n">
-        <v>351891210937.5</v>
+        <v>343052812500</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3084528125</v>
+        <v>0.32087828125</v>
       </c>
     </row>
   </sheetData>
@@ -3876,75 +3888,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39571</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39661</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40067</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -3980,13 +3992,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39662</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39752</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40150</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -4022,13 +4034,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39844</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39934</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40339</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -4064,13 +4076,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39935</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40067</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -4106,13 +4118,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40026</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40150</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -4148,13 +4160,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40117</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40207</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40617</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -4181,7 +4193,7 @@
       <c r="I7" t="n">
         <v>0.2048698402969434</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40617</v>
       </c>
       <c r="K7" t="n">
@@ -4194,13 +4206,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40208</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40339</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -4227,7 +4239,7 @@
       <c r="I8" t="n">
         <v>0.210482712633846</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40617</v>
       </c>
       <c r="K8" t="n">
@@ -4240,13 +4252,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40299</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -4273,7 +4285,7 @@
       <c r="I9" t="n">
         <v>0.2217084573076511</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40617</v>
       </c>
       <c r="K9" t="n">
@@ -4286,13 +4298,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40390</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40514</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -4319,7 +4331,7 @@
       <c r="I10" t="n">
         <v>0.2918693615189331</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40617</v>
       </c>
       <c r="K10" t="n">
@@ -4332,13 +4344,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40481</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40571</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40617</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -4365,7 +4377,7 @@
       <c r="I11" t="n">
         <v>0.3788688827409227</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40617</v>
       </c>
       <c r="K11" t="n">
@@ -4378,13 +4390,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40572</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40689</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -4411,7 +4423,7 @@
       <c r="I12" t="n">
         <v>0.4686748401313636</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40689</v>
       </c>
       <c r="K12" t="n">
@@ -4424,13 +4436,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40663</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40780</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -4457,7 +4469,7 @@
       <c r="I13" t="n">
         <v>0.5248035635003891</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40780</v>
       </c>
       <c r="K13" t="n">
@@ -4470,13 +4482,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40754</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -4503,7 +4515,7 @@
       <c r="I14" t="n">
         <v>0.5444486166795481</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="K14" t="n">
@@ -4516,13 +4528,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40845</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40942</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40981</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -4549,7 +4561,7 @@
       <c r="I15" t="n">
         <v>0.5304164358372918</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40981</v>
       </c>
       <c r="K15" t="n">
@@ -4562,13 +4574,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40943</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41033</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -4595,7 +4607,7 @@
       <c r="I16" t="n">
         <v>0.4939327656474252</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="K16" t="n">
@@ -4608,13 +4620,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41034</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41124</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41150</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -4641,7 +4653,7 @@
       <c r="I17" t="n">
         <v>0.4770941486367175</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41150</v>
       </c>
       <c r="K17" t="n">
@@ -4654,13 +4666,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41125</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41215</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41246</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -4687,7 +4699,7 @@
       <c r="I18" t="n">
         <v>0.4153525529307893</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41246</v>
       </c>
       <c r="K18" t="n">
@@ -4700,13 +4712,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41216</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41345</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -4733,7 +4745,7 @@
       <c r="I19" t="n">
         <v>0.3788688827409227</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41345</v>
       </c>
       <c r="K19" t="n">
@@ -4746,13 +4758,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41307</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41397</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41437</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -4779,7 +4791,7 @@
       <c r="I20" t="n">
         <v>0.2974822338558356</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41437</v>
       </c>
       <c r="K20" t="n">
@@ -4792,13 +4804,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41398</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41488</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41514</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -4825,7 +4837,7 @@
       <c r="I21" t="n">
         <v>0.2132891488022972</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41514</v>
       </c>
       <c r="K21" t="n">
@@ -4838,13 +4850,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42125</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42531</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -4880,13 +4892,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42126</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42216</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42619</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -4922,13 +4934,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42399</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42531</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -4964,13 +4976,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42490</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42619</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -5006,13 +5018,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>43498</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>43588</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>43626</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -5048,13 +5060,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43589</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43679</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>43718</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -5090,13 +5102,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43680</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>43808</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -5132,13 +5144,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43771</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>43917</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -5165,7 +5177,7 @@
       <c r="I29" t="n">
         <v>3.056259503294475</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>43917</v>
       </c>
       <c r="K29" t="n">
@@ -5178,13 +5190,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43862</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>43990</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -5211,7 +5223,7 @@
       <c r="I30" t="n">
         <v>2.959959452610238</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>43990</v>
       </c>
       <c r="K30" t="n">
@@ -5224,13 +5236,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43953</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -5257,7 +5269,7 @@
       <c r="I31" t="n">
         <v>1.388748099341105</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="K31" t="n">
@@ -5270,13 +5282,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>44044</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>44134</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>44172</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -5303,7 +5315,7 @@
       <c r="I32" t="n">
         <v>1.601621895590472</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>44172</v>
       </c>
       <c r="K32" t="n">
@@ -5316,13 +5328,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>44135</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -5349,7 +5361,7 @@
       <c r="I33" t="n">
         <v>2.13887480993411</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="K33" t="n">
@@ -5362,13 +5374,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>44226</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>44354</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -5395,7 +5407,7 @@
       <c r="I34" t="n">
         <v>2.615306639635073</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>44354</v>
       </c>
       <c r="K34" t="n">
@@ -5408,13 +5420,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>44317</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -5441,7 +5453,7 @@
       <c r="I35" t="n">
         <v>2.453117080587937</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="K35" t="n">
@@ -5454,13 +5466,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>44408</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -5487,7 +5499,7 @@
       <c r="I36" t="n">
         <v>6.775727318803852</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="K36" t="n">
@@ -5500,13 +5512,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>44499</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>44589</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>44644</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -5533,7 +5545,7 @@
       <c r="I37" t="n">
         <v>6.26</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>44644</v>
       </c>
       <c r="K37" t="n">
@@ -5546,13 +5558,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44590</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>44718</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -5579,7 +5591,7 @@
       <c r="I38" t="n">
         <v>7.061627093973774</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>44718</v>
       </c>
       <c r="K38" t="n">
@@ -5592,13 +5604,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44681</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -5625,7 +5637,7 @@
       <c r="I39" t="n">
         <v>7.206263795403338</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="K39" t="n">
@@ -5638,13 +5650,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44772</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>44900</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -5671,7 +5683,7 @@
       <c r="I40" t="n">
         <v>2.666008075349502</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>44900</v>
       </c>
       <c r="K40" t="n">
@@ -5684,13 +5696,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44863</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44960</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>45015</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -5717,7 +5729,7 @@
       <c r="I41" t="n">
         <v>3.196329492838863</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>45015</v>
       </c>
       <c r="K41" t="n">
@@ -5730,13 +5742,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44961</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>45051</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>45089</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -5763,7 +5775,7 @@
       <c r="I42" t="n">
         <v>2.611970518479888</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>45089</v>
       </c>
       <c r="K42" t="n">
@@ -5776,13 +5788,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>45052</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>45142</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>45181</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -5809,7 +5821,7 @@
       <c r="I43" t="n">
         <v>2.565149326426908</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>45181</v>
       </c>
       <c r="K43" t="n">
@@ -5822,13 +5834,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>45143</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>45233</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -5855,7 +5867,7 @@
       <c r="I44" t="n">
         <v>3.595405046480744</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="K44" t="n">
@@ -5868,13 +5880,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>45234</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>45324</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -5901,7 +5913,7 @@
       <c r="I45" t="n">
         <v>4.356086956521739</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="K45" t="n">
@@ -5914,13 +5926,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>45325</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>45415</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>45454</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -5947,7 +5959,7 @@
       <c r="I46" t="n">
         <v>4.886086956521739</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>45454</v>
       </c>
       <c r="K46" t="n">
@@ -5960,13 +5972,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>45416</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>45506</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>45545</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -5993,7 +6005,7 @@
       <c r="I47" t="n">
         <v>5.42608695652174</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>45545</v>
       </c>
       <c r="K47" t="n">
@@ -6006,13 +6018,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>45507</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -6039,7 +6051,7 @@
       <c r="I48" t="n">
         <v>5.646086956521739</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="K48" t="n">
@@ -6052,13 +6064,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45598</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>45741</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -6085,7 +6097,7 @@
       <c r="I49" t="n">
         <v>6.22</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>45741</v>
       </c>
       <c r="K49" t="n">
@@ -6098,13 +6110,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45689</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45779</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -6131,7 +6143,7 @@
       <c r="I50" t="n">
         <v>6.27</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="K50" t="n">
@@ -6144,13 +6156,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45780</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -6177,7 +6189,7 @@
       <c r="I51" t="n">
         <v>6.8</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="K51" t="n">
@@ -6190,13 +6202,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45871</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>46000</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -6223,7 +6235,7 @@
       <c r="I52" t="n">
         <v>7.5</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>46000</v>
       </c>
       <c r="K52" t="n">
@@ -6236,13 +6248,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45962</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -6269,7 +6281,7 @@
       <c r="I53" t="n">
         <v>8.68</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="K53" t="n">
@@ -6282,13 +6294,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>46182</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -6315,7 +6327,7 @@
       <c r="I54" t="n">
         <v>12.55</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>46182</v>
       </c>
       <c r="K54" t="n">
@@ -6328,13 +6340,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>46144</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -6361,7 +6373,7 @@
       <c r="I55" t="n">
         <v>17.19</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="K55" t="n">
@@ -6398,52 +6410,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40025</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40067</v>
       </c>
       <c r="C2" t="n">
@@ -6472,10 +6484,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39843</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40067</v>
       </c>
       <c r="C3" t="n">
@@ -6504,10 +6516,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40116</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40150</v>
       </c>
       <c r="C4" t="n">
@@ -6536,10 +6548,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40207</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40255</v>
       </c>
       <c r="C5" t="n">
@@ -6568,10 +6580,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40298</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40339</v>
       </c>
       <c r="C6" t="n">
@@ -6600,10 +6612,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40389</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="C7" t="n">
@@ -6632,10 +6644,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40480</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40514</v>
       </c>
       <c r="C8" t="n">
@@ -6664,10 +6676,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40571</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40617</v>
       </c>
       <c r="C9" t="n">
@@ -6696,10 +6708,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40662</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40689</v>
       </c>
       <c r="C10" t="n">
@@ -6728,10 +6740,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40753</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40780</v>
       </c>
       <c r="C11" t="n">
@@ -6760,10 +6772,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40844</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40870</v>
       </c>
       <c r="C12" t="n">
@@ -6792,10 +6804,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40942</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40981</v>
       </c>
       <c r="C13" t="n">
@@ -6824,10 +6836,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41033</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="C14" t="n">
@@ -6856,10 +6868,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41124</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41150</v>
       </c>
       <c r="C15" t="n">
@@ -6888,10 +6900,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41215</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41246</v>
       </c>
       <c r="C16" t="n">
@@ -6920,10 +6932,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41345</v>
       </c>
       <c r="C17" t="n">
@@ -6952,10 +6964,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41397</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41437</v>
       </c>
       <c r="C18" t="n">
@@ -6984,10 +6996,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41488</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41514</v>
       </c>
       <c r="C19" t="n">
@@ -7016,10 +7028,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>42531</v>
       </c>
       <c r="C20" t="n">
@@ -7048,10 +7060,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>42489</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42531</v>
       </c>
       <c r="C21" t="n">
@@ -7080,10 +7092,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42580</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42619</v>
       </c>
       <c r="C22" t="n">
@@ -7112,10 +7124,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42671</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42713</v>
       </c>
       <c r="C23" t="n">
@@ -7144,10 +7156,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42769</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="C24" t="n">
@@ -7176,10 +7188,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42860</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42895</v>
       </c>
       <c r="C25" t="n">
@@ -7208,10 +7220,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42951</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42986</v>
       </c>
       <c r="C26" t="n">
@@ -7240,10 +7252,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>43042</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>43081</v>
       </c>
       <c r="C27" t="n">
@@ -7272,10 +7284,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>43133</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>43188</v>
       </c>
       <c r="C28" t="n">
@@ -7304,10 +7316,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>43224</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>43263</v>
       </c>
       <c r="C29" t="n">
@@ -7336,10 +7348,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>43315</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>43354</v>
       </c>
       <c r="C30" t="n">
@@ -7368,10 +7380,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>43406</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>43444</v>
       </c>
       <c r="C31" t="n">
@@ -7400,10 +7412,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43553</v>
       </c>
       <c r="C32" t="n">
@@ -7432,10 +7444,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43588</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43626</v>
       </c>
       <c r="C33" t="n">
@@ -7464,10 +7476,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43679</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43718</v>
       </c>
       <c r="C34" t="n">
@@ -7496,10 +7508,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43770</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43808</v>
       </c>
       <c r="C35" t="n">
@@ -7528,10 +7540,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43917</v>
       </c>
       <c r="C36" t="n">
@@ -7560,10 +7572,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43952</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43990</v>
       </c>
       <c r="C37" t="n">
@@ -7592,10 +7604,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>44043</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>44078</v>
       </c>
       <c r="C38" t="n">
@@ -7624,10 +7636,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>44134</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>44172</v>
       </c>
       <c r="C39" t="n">
@@ -7656,10 +7668,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>44281</v>
       </c>
       <c r="C40" t="n">
@@ -7688,10 +7700,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>44316</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>44354</v>
       </c>
       <c r="C41" t="n">
@@ -7720,10 +7732,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>44407</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>44442</v>
       </c>
       <c r="C42" t="n">
@@ -7752,10 +7764,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>44498</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44533</v>
       </c>
       <c r="C43" t="n">
@@ -7784,10 +7796,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44589</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44644</v>
       </c>
       <c r="C44" t="n">
@@ -7816,10 +7828,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44680</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44718</v>
       </c>
       <c r="C45" t="n">
@@ -7848,10 +7860,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44771</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="C46" t="n">
@@ -7880,10 +7892,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44862</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44900</v>
       </c>
       <c r="C47" t="n">
@@ -7912,10 +7924,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44960</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>45015</v>
       </c>
       <c r="C48" t="n">
@@ -7944,10 +7956,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>45051</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>45089</v>
       </c>
       <c r="C49" t="n">
@@ -7976,10 +7988,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>45142</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>45181</v>
       </c>
       <c r="C50" t="n">
@@ -8008,10 +8020,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>45233</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>45268</v>
       </c>
       <c r="C51" t="n">
@@ -8040,10 +8052,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>45324</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>45376</v>
       </c>
       <c r="C52" t="n">
@@ -8072,10 +8084,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>45415</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>45454</v>
       </c>
       <c r="C53" t="n">
@@ -8104,10 +8116,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>45506</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45545</v>
       </c>
       <c r="C54" t="n">
@@ -8136,10 +8148,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45597</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45636</v>
       </c>
       <c r="C55" t="n">
@@ -8168,10 +8180,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45741</v>
       </c>
       <c r="C56" t="n">
@@ -8200,10 +8212,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45779</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45818</v>
       </c>
       <c r="C57" t="n">
@@ -8232,10 +8244,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45870</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45908</v>
       </c>
       <c r="C58" t="n">
@@ -8264,10 +8276,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>46000</v>
       </c>
       <c r="C59" t="n">
@@ -8296,10 +8308,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>46097</v>
       </c>
       <c r="C60" t="n">
@@ -8328,10 +8340,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>46143</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>46182</v>
       </c>
       <c r="C61" t="n">
@@ -8360,10 +8372,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>46234</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>46273</v>
       </c>
       <c r="C62" t="n">
@@ -8410,12 +8422,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/DELL.xlsx
+++ b/salidas/empresas/DELL.xlsx
@@ -498,7 +498,7 @@
         <v>42613</v>
       </c>
       <c r="B2" t="n">
-        <v>11.39071178436279</v>
+        <v>11.39071273803711</v>
       </c>
       <c r="C2" t="n">
         <v>12.53915691375732</v>
@@ -523,7 +523,7 @@
         <v>42643</v>
       </c>
       <c r="B3" t="n">
-        <v>12.18612670898438</v>
+        <v>12.18612575531006</v>
       </c>
       <c r="C3" t="n">
         <v>13.41476535797119</v>
@@ -548,7 +548,7 @@
         <v>42674</v>
       </c>
       <c r="B4" t="n">
-        <v>12.5149974822998</v>
+        <v>12.51499938964844</v>
       </c>
       <c r="C4" t="n">
         <v>13.77679538726807</v>
@@ -573,7 +573,7 @@
         <v>42704</v>
       </c>
       <c r="B5" t="n">
-        <v>13.65458011627197</v>
+        <v>13.65457916259766</v>
       </c>
       <c r="C5" t="n">
         <v>15.03127193450928</v>
@@ -598,7 +598,7 @@
         <v>42735</v>
       </c>
       <c r="B6" t="n">
-        <v>14.01404571533203</v>
+        <v>14.01404476165771</v>
       </c>
       <c r="C6" t="n">
         <v>15.42698001861572</v>
@@ -623,7 +623,7 @@
         <v>42766</v>
       </c>
       <c r="B7" t="n">
-        <v>16.05865859985352</v>
+        <v>16.05866241455078</v>
       </c>
       <c r="C7" t="n">
         <v>17.6777400970459</v>
@@ -698,7 +698,7 @@
         <v>42855</v>
       </c>
       <c r="B10" t="n">
-        <v>17.10901069641113</v>
+        <v>17.1090202331543</v>
       </c>
       <c r="C10" t="n">
         <v>18.83399391174316</v>
@@ -723,7 +723,7 @@
         <v>42886</v>
       </c>
       <c r="B11" t="n">
-        <v>17.69028282165527</v>
+        <v>17.69027709960938</v>
       </c>
       <c r="C11" t="n">
         <v>19.47386169433594</v>
@@ -748,7 +748,7 @@
         <v>42916</v>
       </c>
       <c r="B12" t="n">
-        <v>15.57937812805176</v>
+        <v>15.57937717437744</v>
       </c>
       <c r="C12" t="n">
         <v>17.15013122558594</v>
@@ -773,7 +773,7 @@
         <v>42947</v>
       </c>
       <c r="B13" t="n">
-        <v>16.38498687744141</v>
+        <v>16.38498306274414</v>
       </c>
       <c r="C13" t="n">
         <v>18.03696441650391</v>
@@ -798,7 +798,7 @@
         <v>42978</v>
       </c>
       <c r="B14" t="n">
-        <v>19.1026439666748</v>
+        <v>19.10264587402344</v>
       </c>
       <c r="C14" t="n">
         <v>21.02862548828125</v>
@@ -823,7 +823,7 @@
         <v>43008</v>
       </c>
       <c r="B15" t="n">
-        <v>19.68390846252441</v>
+        <v>19.68390655517578</v>
       </c>
       <c r="C15" t="n">
         <v>21.66849327087402</v>
@@ -873,7 +873,7 @@
         <v>43069</v>
       </c>
       <c r="B17" t="n">
-        <v>19.94649505615234</v>
+        <v>19.94649887084961</v>
       </c>
       <c r="C17" t="n">
         <v>21.95755767822266</v>
@@ -898,7 +898,7 @@
         <v>43100</v>
       </c>
       <c r="B18" t="n">
-        <v>20.72150993347168</v>
+        <v>20.72151184082031</v>
       </c>
       <c r="C18" t="n">
         <v>22.81071281433105</v>
@@ -923,7 +923,7 @@
         <v>43131</v>
       </c>
       <c r="B19" t="n">
-        <v>18.2791862487793</v>
+        <v>18.2791919708252</v>
       </c>
       <c r="C19" t="n">
         <v>20.12214660644531</v>
@@ -948,7 +948,7 @@
         <v>43159</v>
       </c>
       <c r="B20" t="n">
-        <v>18.93948173522949</v>
+        <v>18.93947982788086</v>
       </c>
       <c r="C20" t="n">
         <v>20.84901428222656</v>
@@ -973,7 +973,7 @@
         <v>43190</v>
       </c>
       <c r="B21" t="n">
-        <v>18.66414833068848</v>
+        <v>18.66414642333984</v>
       </c>
       <c r="C21" t="n">
         <v>20.54591941833496</v>
@@ -998,7 +998,7 @@
         <v>43220</v>
       </c>
       <c r="B22" t="n">
-        <v>18.29703712463379</v>
+        <v>18.29703521728516</v>
       </c>
       <c r="C22" t="n">
         <v>20.14179229736328</v>
@@ -1073,7 +1073,7 @@
         <v>43312</v>
       </c>
       <c r="B25" t="n">
-        <v>23.5870361328125</v>
+        <v>23.58703804016113</v>
       </c>
       <c r="C25" t="n">
         <v>25.96514701843262</v>
@@ -1123,7 +1123,7 @@
         <v>43373</v>
       </c>
       <c r="B27" t="n">
-        <v>24.7597599029541</v>
+        <v>24.75975799560547</v>
       </c>
       <c r="C27" t="n">
         <v>27.25610733032227</v>
@@ -1148,7 +1148,7 @@
         <v>43404</v>
       </c>
       <c r="B28" t="n">
-        <v>23.04401206970215</v>
+        <v>23.04401779174805</v>
       </c>
       <c r="C28" t="n">
         <v>25.36737632751465</v>
@@ -1198,7 +1198,7 @@
         <v>43465</v>
       </c>
       <c r="B30" t="n">
-        <v>22.50079345703125</v>
+        <v>22.50079154968262</v>
       </c>
       <c r="C30" t="n">
         <v>24.76938629150391</v>
@@ -1248,7 +1248,7 @@
         <v>43524</v>
       </c>
       <c r="B32" t="n">
-        <v>25.70071983337402</v>
+        <v>25.70072174072266</v>
       </c>
       <c r="C32" t="n">
         <v>28.29194068908691</v>
@@ -1273,7 +1273,7 @@
         <v>43555</v>
       </c>
       <c r="B33" t="n">
-        <v>27.02213287353516</v>
+        <v>27.02212905883789</v>
       </c>
       <c r="C33" t="n">
         <v>29.74657821655273</v>
@@ -1298,7 +1298,7 @@
         <v>43585</v>
       </c>
       <c r="B34" t="n">
-        <v>31.03700256347656</v>
+        <v>31.03701400756836</v>
       </c>
       <c r="C34" t="n">
         <v>34.16624450683594</v>
@@ -1323,7 +1323,7 @@
         <v>43616</v>
       </c>
       <c r="B35" t="n">
-        <v>27.41810035705566</v>
+        <v>27.41809463500977</v>
       </c>
       <c r="C35" t="n">
         <v>30.18246269226074</v>
@@ -1348,7 +1348,7 @@
         <v>43646</v>
       </c>
       <c r="B36" t="n">
-        <v>23.389404296875</v>
+        <v>23.38940811157227</v>
       </c>
       <c r="C36" t="n">
         <v>25.74759292602539</v>
@@ -1398,7 +1398,7 @@
         <v>43708</v>
       </c>
       <c r="B38" t="n">
-        <v>23.72551155090332</v>
+        <v>23.72551345825195</v>
       </c>
       <c r="C38" t="n">
         <v>26.11758613586426</v>
@@ -1423,7 +1423,7 @@
         <v>43738</v>
       </c>
       <c r="B39" t="n">
-        <v>23.87745475769043</v>
+        <v>23.8774585723877</v>
       </c>
       <c r="C39" t="n">
         <v>26.28484535217285</v>
@@ -1498,7 +1498,7 @@
         <v>43830</v>
       </c>
       <c r="B42" t="n">
-        <v>23.66105842590332</v>
+        <v>23.66105461120605</v>
       </c>
       <c r="C42" t="n">
         <v>26.04662895202637</v>
@@ -1548,7 +1548,7 @@
         <v>43890</v>
       </c>
       <c r="B44" t="n">
-        <v>18.62864303588867</v>
+        <v>18.6286506652832</v>
       </c>
       <c r="C44" t="n">
         <v>20.5068416595459</v>
@@ -1573,7 +1573,7 @@
         <v>43921</v>
       </c>
       <c r="B45" t="n">
-        <v>18.20966720581055</v>
+        <v>18.20967102050781</v>
       </c>
       <c r="C45" t="n">
         <v>20.04561614990234</v>
@@ -1631,7 +1631,7 @@
         <v>43982</v>
       </c>
       <c r="B47" t="n">
-        <v>22.85531997680664</v>
+        <v>22.85531806945801</v>
       </c>
       <c r="C47" t="n">
         <v>25.15965461730957</v>
@@ -1689,7 +1689,7 @@
         <v>44043</v>
       </c>
       <c r="B49" t="n">
-        <v>27.54701805114746</v>
+        <v>27.5470142364502</v>
       </c>
       <c r="C49" t="n">
         <v>30.32437896728516</v>
@@ -1718,7 +1718,7 @@
         <v>44074</v>
       </c>
       <c r="B50" t="n">
-        <v>30.42465019226074</v>
+        <v>30.42464828491211</v>
       </c>
       <c r="C50" t="n">
         <v>33.49214553833008</v>
@@ -1747,7 +1747,7 @@
         <v>44104</v>
       </c>
       <c r="B51" t="n">
-        <v>31.16592407226562</v>
+        <v>31.16592597961426</v>
       </c>
       <c r="C51" t="n">
         <v>34.30815887451172</v>
@@ -1776,7 +1776,7 @@
         <v>44135</v>
       </c>
       <c r="B52" t="n">
-        <v>27.74499320983887</v>
+        <v>27.7449951171875</v>
       </c>
       <c r="C52" t="n">
         <v>30.54232025146484</v>
@@ -1805,7 +1805,7 @@
         <v>44165</v>
       </c>
       <c r="B53" t="n">
-        <v>31.78289413452148</v>
+        <v>31.78288841247559</v>
       </c>
       <c r="C53" t="n">
         <v>34.98732757568359</v>
@@ -1863,7 +1863,7 @@
         <v>44227</v>
       </c>
       <c r="B55" t="n">
-        <v>33.56011581420898</v>
+        <v>33.56011199951172</v>
       </c>
       <c r="C55" t="n">
         <v>36.94374084472656</v>
@@ -1892,7 +1892,7 @@
         <v>44255</v>
       </c>
       <c r="B56" t="n">
-        <v>37.32636260986328</v>
+        <v>37.32636642456055</v>
       </c>
       <c r="C56" t="n">
         <v>41.0897102355957</v>
@@ -1921,7 +1921,7 @@
         <v>44286</v>
       </c>
       <c r="B57" t="n">
-        <v>40.58614349365234</v>
+        <v>40.58614730834961</v>
       </c>
       <c r="C57" t="n">
         <v>44.67815399169922</v>
@@ -1950,7 +1950,7 @@
         <v>44316</v>
       </c>
       <c r="B58" t="n">
-        <v>45.27324295043945</v>
+        <v>45.27323150634766</v>
       </c>
       <c r="C58" t="n">
         <v>49.83781051635742</v>
@@ -1979,7 +1979,7 @@
         <v>44347</v>
       </c>
       <c r="B59" t="n">
-        <v>45.41596603393555</v>
+        <v>45.41596984863281</v>
       </c>
       <c r="C59" t="n">
         <v>49.99493026733398</v>
@@ -2008,7 +2008,7 @@
         <v>44377</v>
       </c>
       <c r="B60" t="n">
-        <v>45.89020538330078</v>
+        <v>45.89021301269531</v>
       </c>
       <c r="C60" t="n">
         <v>50.5169792175293</v>
@@ -2066,7 +2066,7 @@
         <v>44439</v>
       </c>
       <c r="B62" t="n">
-        <v>44.8726806640625</v>
+        <v>44.87267303466797</v>
       </c>
       <c r="C62" t="n">
         <v>49.39685821533203</v>
@@ -2095,7 +2095,7 @@
         <v>44469</v>
       </c>
       <c r="B63" t="n">
-        <v>47.90225219726562</v>
+        <v>47.90224456787109</v>
       </c>
       <c r="C63" t="n">
         <v>52.73188018798828</v>
@@ -2153,7 +2153,7 @@
         <v>44530</v>
       </c>
       <c r="B65" t="n">
-        <v>51.29799652099609</v>
+        <v>51.2979850769043</v>
       </c>
       <c r="C65" t="n">
         <v>56.47000122070312</v>
@@ -2182,7 +2182,7 @@
         <v>44561</v>
       </c>
       <c r="B66" t="n">
-        <v>51.02547454833984</v>
+        <v>51.02547073364258</v>
       </c>
       <c r="C66" t="n">
         <v>56.16999816894531</v>
@@ -2211,7 +2211,7 @@
         <v>44592</v>
       </c>
       <c r="B67" t="n">
-        <v>51.60686111450195</v>
+        <v>51.60685348510742</v>
       </c>
       <c r="C67" t="n">
         <v>56.81000137329102</v>
@@ -2240,7 +2240,7 @@
         <v>44620</v>
       </c>
       <c r="B68" t="n">
-        <v>46.29264068603516</v>
+        <v>46.29264831542969</v>
       </c>
       <c r="C68" t="n">
         <v>50.95999908447266</v>
@@ -2269,7 +2269,7 @@
         <v>44651</v>
       </c>
       <c r="B69" t="n">
-        <v>45.59317398071289</v>
+        <v>45.59318161010742</v>
       </c>
       <c r="C69" t="n">
         <v>50.18999862670898</v>
@@ -2298,7 +2298,7 @@
         <v>44681</v>
       </c>
       <c r="B70" t="n">
-        <v>43.00356674194336</v>
+        <v>43.00355911254883</v>
       </c>
       <c r="C70" t="n">
         <v>47.0099983215332</v>
@@ -2327,7 +2327,7 @@
         <v>44712</v>
       </c>
       <c r="B71" t="n">
-        <v>45.68384552001953</v>
+        <v>45.68385314941406</v>
       </c>
       <c r="C71" t="n">
         <v>49.93999862670898</v>
@@ -2356,7 +2356,7 @@
         <v>44742</v>
       </c>
       <c r="B72" t="n">
-        <v>42.27173233032227</v>
+        <v>42.27174377441406</v>
       </c>
       <c r="C72" t="n">
         <v>46.20999908447266</v>
@@ -2385,7 +2385,7 @@
         <v>44773</v>
       </c>
       <c r="B73" t="n">
-        <v>41.53929138183594</v>
+        <v>41.53928375244141</v>
       </c>
       <c r="C73" t="n">
         <v>45.06000137329102</v>
@@ -2443,7 +2443,7 @@
         <v>44834</v>
       </c>
       <c r="B75" t="n">
-        <v>31.50016784667969</v>
+        <v>31.50016593933105</v>
       </c>
       <c r="C75" t="n">
         <v>34.16999816894531</v>
@@ -2530,7 +2530,7 @@
         <v>44926</v>
       </c>
       <c r="B78" t="n">
-        <v>37.43585586547852</v>
+        <v>37.43584060668945</v>
       </c>
       <c r="C78" t="n">
         <v>40.22000122070312</v>
@@ -2559,7 +2559,7 @@
         <v>44957</v>
       </c>
       <c r="B79" t="n">
-        <v>38.11463165283203</v>
+        <v>38.11463928222656</v>
       </c>
       <c r="C79" t="n">
         <v>40.61999893188477</v>
@@ -2588,7 +2588,7 @@
         <v>44985</v>
       </c>
       <c r="B80" t="n">
-        <v>38.13339996337891</v>
+        <v>38.13339614868164</v>
       </c>
       <c r="C80" t="n">
         <v>40.63999938964844</v>
@@ -2617,7 +2617,7 @@
         <v>45016</v>
       </c>
       <c r="B81" t="n">
-        <v>37.72993087768555</v>
+        <v>37.72992706298828</v>
       </c>
       <c r="C81" t="n">
         <v>40.20999908447266</v>
@@ -2646,7 +2646,7 @@
         <v>45046</v>
       </c>
       <c r="B82" t="n">
-        <v>41.16089630126953</v>
+        <v>41.16089248657227</v>
       </c>
       <c r="C82" t="n">
         <v>43.4900016784668</v>
@@ -2675,7 +2675,7 @@
         <v>45077</v>
       </c>
       <c r="B83" t="n">
-        <v>42.41020584106445</v>
+        <v>42.41019821166992</v>
       </c>
       <c r="C83" t="n">
         <v>44.81000137329102</v>
@@ -2733,7 +2733,7 @@
         <v>45138</v>
       </c>
       <c r="B85" t="n">
-        <v>50.43426895141602</v>
+        <v>50.43427276611328</v>
       </c>
       <c r="C85" t="n">
         <v>52.91999816894531</v>
@@ -2762,7 +2762,7 @@
         <v>45169</v>
       </c>
       <c r="B86" t="n">
-        <v>53.59833526611328</v>
+        <v>53.59833145141602</v>
       </c>
       <c r="C86" t="n">
         <v>56.2400016784668</v>
@@ -2791,7 +2791,7 @@
         <v>45199</v>
       </c>
       <c r="B87" t="n">
-        <v>65.66366577148438</v>
+        <v>65.66365814208984</v>
       </c>
       <c r="C87" t="n">
         <v>68.90000152587891</v>
@@ -2820,7 +2820,7 @@
         <v>45230</v>
       </c>
       <c r="B88" t="n">
-        <v>64.12714385986328</v>
+        <v>64.12713623046875</v>
       </c>
       <c r="C88" t="n">
         <v>66.91000366210938</v>
@@ -2878,7 +2878,7 @@
         <v>45291</v>
       </c>
       <c r="B90" t="n">
-        <v>73.31828308105469</v>
+        <v>73.31827545166016</v>
       </c>
       <c r="C90" t="n">
         <v>76.5</v>
@@ -2936,7 +2936,7 @@
         <v>45351</v>
       </c>
       <c r="B92" t="n">
-        <v>91.1282958984375</v>
+        <v>91.12830352783203</v>
       </c>
       <c r="C92" t="n">
         <v>94.66000366210938</v>
@@ -2965,7 +2965,7 @@
         <v>45382</v>
       </c>
       <c r="B93" t="n">
-        <v>109.8526229858398</v>
+        <v>109.8526306152344</v>
       </c>
       <c r="C93" t="n">
         <v>114.1100006103516</v>
@@ -2994,7 +2994,7 @@
         <v>45412</v>
       </c>
       <c r="B94" t="n">
-        <v>120.4563980102539</v>
+        <v>120.4563903808594</v>
       </c>
       <c r="C94" t="n">
         <v>124.6399993896484</v>
@@ -3023,7 +3023,7 @@
         <v>45443</v>
       </c>
       <c r="B95" t="n">
-        <v>134.8755798339844</v>
+        <v>134.8756103515625</v>
       </c>
       <c r="C95" t="n">
         <v>139.5599975585938</v>
@@ -3052,7 +3052,7 @@
         <v>45473</v>
       </c>
       <c r="B96" t="n">
-        <v>133.2809906005859</v>
+        <v>133.2809753417969</v>
       </c>
       <c r="C96" t="n">
         <v>137.9100036621094</v>
@@ -3081,7 +3081,7 @@
         <v>45504</v>
       </c>
       <c r="B97" t="n">
-        <v>110.2453536987305</v>
+        <v>110.2453460693359</v>
       </c>
       <c r="C97" t="n">
         <v>113.6800003051758</v>
@@ -3139,7 +3139,7 @@
         <v>45565</v>
       </c>
       <c r="B99" t="n">
-        <v>114.9585037231445</v>
+        <v>114.9585189819336</v>
       </c>
       <c r="C99" t="n">
         <v>118.5400009155273</v>
@@ -3168,7 +3168,7 @@
         <v>45596</v>
       </c>
       <c r="B100" t="n">
-        <v>120.3208160400391</v>
+        <v>120.3208084106445</v>
       </c>
       <c r="C100" t="n">
         <v>123.629997253418</v>
@@ -3284,7 +3284,7 @@
         <v>45716</v>
       </c>
       <c r="B104" t="n">
-        <v>100.4100036621094</v>
+        <v>100.4099960327148</v>
       </c>
       <c r="C104" t="n">
         <v>102.7600021362305</v>
@@ -3313,7 +3313,7 @@
         <v>45747</v>
       </c>
       <c r="B105" t="n">
-        <v>89.06550598144531</v>
+        <v>89.06549835205078</v>
       </c>
       <c r="C105" t="n">
         <v>91.15000152587891</v>
@@ -3400,7 +3400,7 @@
         <v>45838</v>
       </c>
       <c r="B108" t="n">
-        <v>120.5645294189453</v>
+        <v>120.5645370483398</v>
       </c>
       <c r="C108" t="n">
         <v>122.5999984741211</v>
